--- a/planering/biologi-omrade2/biologi-2-kahoot.xlsx
+++ b/planering/biologi-omrade2/biologi-2-kahoot.xlsx
@@ -1880,12 +1880,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
+          <t>Atomen</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
           <t>Vävnaden</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Atomen</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
+          <t>Louis Pasteur</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Robert Hooke</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Carl von Linné</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
           <t>Charles Darwin</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Robert Hooke</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Carl von Linné</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Louis Pasteur</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
+          <t>50 gånger</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>40 gånger</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>400 gånger</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
           <t>4 000 gånger</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>40 gånger</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>400 gånger</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>50 gånger</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
+          <t>Ribosomen</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Cellväggen</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
           <t>Vakuolen</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Ribosomen</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>Cellväggen</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
+          <t>Cellmembran</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
           <t>Cellkärna</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Cellmembran</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
+          <t>Djurcellen har cellvägg</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
           <t>Bakterien har kloroplaster</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Djurcellen har cellvägg</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -2274,17 +2274,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
+          <t>De lagrar vatten</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>De gör fotosyntes</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
           <t>De skyddar cellen</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>De lagrar vatten</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>De gör fotosyntes</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
+          <t>Jäsning</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Fotosyntes</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
           <t>Pollinering</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Jäsning</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>Fotosyntes</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
+          <t>Cellulosa</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Klorofyll</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
           <t>Etanol</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Klorofyll</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Cellulosa</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2445,22 +2445,22 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
+          <t>Glukos och koldioxid</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Syre och vatten</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Koldioxid och vatten</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
           <t>Syre och glukos</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Syre och vatten</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Koldioxid och vatten</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>Glukos och koldioxid</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
+          <t>Koldioxid + vatten → glukos + syre</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Glukos + koldioxid → syre + energi</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Glukos + syre → koldioxid + vatten + energi</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
           <t>Syre + vatten → glukos + energi</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Glukos + koldioxid → syre + energi</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Glukos + syre → koldioxid + vatten + energi</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Koldioxid + vatten → glukos + syre</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
+          <t>Bara om de har blommor</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
           <t>Nej, bara på dagen</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Bara om de har blommor</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
+          <t>Cell, organ, vävnad, organsystem</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Cell, vävnad, organ, organsystem</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
           <t>Vävnad, cell, organ, organsystem</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Cell, vävnad, organ, organsystem</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Cell, organ, vävnad, organsystem</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
+          <t>Syre till roten</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
           <t>Pollen till blomman</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Socker nedåt från bladen</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Syre till roten</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
